--- a/src/main/resources/projects.xlsx
+++ b/src/main/resources/projects.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java\projectStart\projectStart\src\main\java\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java\projectStart\projectStart\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D55DC8A-3D47-4E56-B3A5-490CBD515140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352A31D6-E9B9-4E6C-A770-F97039A38DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11535" yWindow="2190" windowWidth="14640" windowHeight="10410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -444,7 +444,7 @@
         <v>36649</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
